--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484569_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484569_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5516</v>
+        <v>7.9342</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0636</v>
+        <v>6.1737</v>
       </c>
       <c r="F2" t="n">
-        <v>1.488</v>
+        <v>1.7605</v>
       </c>
       <c r="G2" t="n">
         <v>3.1685</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6615</v>
+        <v>-0.2789</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.589</v>
+        <v>-0.4789</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0725</v>
+        <v>0.2</v>
       </c>
       <c r="V2" t="n">
         <v>2.8455</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.707</v>
+        <v>5.5887</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5849</v>
+        <v>3.6399</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1221</v>
+        <v>1.9487</v>
       </c>
       <c r="G3" t="n">
         <v>3.2532</v>
@@ -688,13 +688,13 @@
         <v>1.4661</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5907</v>
+        <v>-0.7091</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8258</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.235</v>
+        <v>0.0616</v>
       </c>
       <c r="V3" t="n">
         <v>1.5785</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6507</v>
+        <v>1.824</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6546</v>
+        <v>0.8031</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9961</v>
+        <v>1.0209</v>
       </c>
       <c r="G4" t="n">
         <v>-1.7398</v>
@@ -766,13 +766,13 @@
         <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>0.969</v>
+        <v>0.1423</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9133</v>
+        <v>0.0619</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0557</v>
+        <v>0.0805</v>
       </c>
       <c r="V4" t="n">
         <v>1.5889</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8526</v>
+        <v>0.9132</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9968</v>
+        <v>1.1069</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1442</v>
+        <v>-0.1937</v>
       </c>
       <c r="G6" t="n">
         <v>0.7281</v>
@@ -922,13 +922,13 @@
         <v>2.0158</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3807</v>
+        <v>-0.3201</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.589</v>
+        <v>-0.4789</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2083</v>
+        <v>0.1587</v>
       </c>
       <c r="V6" t="n">
         <v>0.3219</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.6369</v>
       </c>
       <c r="E7" t="n">
         <v>0.3846</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1532</v>
+        <v>0.2523</v>
       </c>
       <c r="G7" t="n">
         <v>1.4453</v>
@@ -1000,13 +1000,13 @@
         <v>1.4661</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1066</v>
+        <v>-1.0075</v>
       </c>
       <c r="T7" t="n">
         <v>-0.9909</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1157</v>
+        <v>-0.0166</v>
       </c>
       <c r="V7" t="n">
         <v>-1.267</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3245</v>
+        <v>0.2224</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5643</v>
+        <v>-0.4682</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8888</v>
+        <v>0.6906</v>
       </c>
       <c r="G8" t="n">
         <v>-2.7666</v>
@@ -1078,13 +1078,13 @@
         <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6812</v>
+        <v>-0.7832</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.046</v>
+        <v>-0.9498</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3648</v>
+        <v>0.1666</v>
       </c>
       <c r="V8" t="n">
         <v>2.8559</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4559</v>
+        <v>-0.4807</v>
       </c>
       <c r="E10" t="n">
         <v>0.2484</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7043</v>
+        <v>-0.7291</v>
       </c>
       <c r="G10" t="n">
         <v>1.2115</v>
@@ -1234,13 +1234,13 @@
         <v>1.0995</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4999</v>
+        <v>-1.5247</v>
       </c>
       <c r="T10" t="n">
         <v>-1.046</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4539</v>
+        <v>-0.4787</v>
       </c>
       <c r="V10" t="n">
         <v>-1.267</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.235</v>
+        <v>-1.114</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7295</v>
+        <v>-0.6333</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.4807</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3246</v>
@@ -1312,13 +1312,13 @@
         <v>0.1833</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0936</v>
+        <v>0.0273</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1101</v>
+        <v>-0.0139</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8594</v>
+        <v>-2.0921</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6257</v>
+        <v>-3.131</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7663</v>
+        <v>1.0388</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9340000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3206</v>
+        <v>-0.5534</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7896</v>
+        <v>-0.2949</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.531</v>
+        <v>-0.2585</v>
       </c>
       <c r="V12" t="n">
         <v>0.3115</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.9452</v>
+        <v>-7.7533</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.7829</v>
+        <v>-6.3432</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1623</v>
+        <v>-1.4101</v>
       </c>
       <c r="G13" t="n">
         <v>-1.593</v>
@@ -1468,13 +1468,13 @@
         <v>0.5498</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4201</v>
+        <v>-0.2281</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5143</v>
+        <v>-0.0746</v>
       </c>
       <c r="U13" t="n">
-        <v>0.09420000000000001</v>
+        <v>-0.1535</v>
       </c>
       <c r="V13" t="n">
         <v>-1.9005</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2285</v>
+        <v>6.779100000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7646</v>
+        <v>3.315</v>
       </c>
       <c r="F14" t="n">
         <v>3.4639</v>
@@ -1546,13 +1546,13 @@
         <v>13.7445</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.2256</v>
+        <v>-5.6751</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.972799999999999</v>
+        <v>-5.422099999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2529000000000001</v>
+        <v>-0.2529</v>
       </c>
       <c r="V14" t="n">
         <v>6.012700000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7337</v>
+        <v>3.9702</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2145</v>
+        <v>2.5415</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5191</v>
+        <v>1.4287</v>
       </c>
       <c r="G15" t="n">
         <v>4.0803</v>
@@ -1624,13 +1624,13 @@
         <v>1.4661</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3155</v>
+        <v>1.552</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1509</v>
+        <v>0.4778</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1647</v>
+        <v>1.0743</v>
       </c>
       <c r="V15" t="n">
         <v>-2.212</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8469</v>
+        <v>3.0232</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4894</v>
+        <v>1.3932</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3575</v>
+        <v>1.63</v>
       </c>
       <c r="G16" t="n">
         <v>1.3289</v>
@@ -1702,13 +1702,13 @@
         <v>0.5498</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9683</v>
+        <v>1.1446</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6395</v>
+        <v>0.5434</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3287</v>
+        <v>0.6012</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2657</v>
+        <v>-0.3885</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0665</v>
+        <v>-0.5473</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3322</v>
+        <v>0.1587</v>
       </c>
       <c r="G18" t="n">
         <v>-2.065</v>
@@ -1858,13 +1858,13 @@
         <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5036</v>
+        <v>1.8494</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9857</v>
+        <v>0.5049</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5178</v>
+        <v>1.3444</v>
       </c>
       <c r="V18" t="n">
         <v>0.0104</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5796</v>
+        <v>-0.4441</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5147</v>
+        <v>1.4185</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0942</v>
+        <v>-1.8626</v>
       </c>
       <c r="G19" t="n">
         <v>0.8299</v>
@@ -1936,13 +1936,13 @@
         <v>1.0995</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5514</v>
+        <v>0.6868</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1493</v>
+        <v>-0.2454</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7006</v>
+        <v>0.9323</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3115</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. KEITH CAMARA</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8605</v>
+        <v>-0.5103</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.7839</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.2736</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5491</v>
+        <v>-0.0462</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7519</v>
+        <v>-0.6649</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2028</v>
+        <v>0.6187</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3471</v>
+        <v>1.531</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8177</v>
+        <v>0.4952</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1648</v>
+        <v>1.0358</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8962</v>
+        <v>-1.5772</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9342</v>
+        <v>-1.1602</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.962</v>
+        <v>-0.417</v>
       </c>
       <c r="P20" t="n">
+        <v>-0.5498</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-1.8326</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-2.7489</v>
-      </c>
       <c r="R20" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5212</v>
+        <v>0.4076</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6199</v>
+        <v>-0.4928</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9013</v>
+        <v>0.9004</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.3324</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8686</v>
+        <v>-0.6267</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7078</v>
+        <v>-0.5155</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1608</v>
+        <v>-0.1112</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9748</v>
@@ -2092,13 +2092,13 @@
         <v>0.1833</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0771</v>
+        <v>0.1648</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1101</v>
+        <v>0.0822</v>
       </c>
       <c r="U21" t="n">
-        <v>0.033</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9523</v>
+        <v>-0.6434</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.003</v>
+        <v>-2.0991</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0507</v>
+        <v>1.4557</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6947</v>
@@ -2170,13 +2170,13 @@
         <v>0.5498</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1581</v>
+        <v>0.1508</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0196</v>
+        <v>-0.1157</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1385</v>
+        <v>0.2666</v>
       </c>
       <c r="V22" t="n">
         <v>1.267</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>D. KEITH CAMARA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3348</v>
+        <v>-0.8299</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6493</v>
+        <v>-0.9741</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3145</v>
+        <v>0.1443</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0462</v>
+        <v>-0.5491</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6649</v>
+        <v>-1.7519</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6187</v>
+        <v>1.2028</v>
       </c>
       <c r="J23" t="n">
-        <v>1.531</v>
+        <v>1.3471</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4952</v>
+        <v>-0.8177</v>
       </c>
       <c r="L23" t="n">
-        <v>1.0358</v>
+        <v>2.1648</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5772</v>
+        <v>-1.8962</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1602</v>
+        <v>-0.9342</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.417</v>
+        <v>-0.962</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5498</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4169</v>
+        <v>1.5519</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3582</v>
+        <v>0.4276</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9413</v>
+        <v>1.1242</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3101</v>
+        <v>-2.3685</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1817</v>
+        <v>-1.8933</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1284</v>
+        <v>-0.4752</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7659</v>
@@ -2326,13 +2326,13 @@
         <v>0.3665</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3562</v>
+        <v>0.2979</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3854</v>
+        <v>-0.0969</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7416</v>
+        <v>0.3948</v>
       </c>
       <c r="V24" t="n">
         <v>-1.267</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.0986</v>
+        <v>-2.6906</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9823</v>
+        <v>-2.0785</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1163</v>
+        <v>-0.6122</v>
       </c>
       <c r="G25" t="n">
         <v>0.07480000000000001</v>
@@ -2404,13 +2404,13 @@
         <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8069</v>
+        <v>-0.3989</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.405</v>
+        <v>-0.5011</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.402</v>
+        <v>0.1022</v>
       </c>
       <c r="V25" t="n">
         <v>-1.267</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.6456</v>
+        <v>-5.0132</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.8854</v>
+        <v>-1.5008</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.7602</v>
+        <v>-3.5125</v>
       </c>
       <c r="G26" t="n">
         <v>-2.6533</v>
@@ -2482,13 +2482,13 @@
         <v>0.3665</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5317</v>
+        <v>0.1007</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7157</v>
+        <v>-0.3311</v>
       </c>
       <c r="U26" t="n">
-        <v>0.184</v>
+        <v>0.4317</v>
       </c>
       <c r="V26" t="n">
         <v>-1.9109</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.2285</v>
+        <v>-4.946500000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.463900000000001</v>
+        <v>-3.464</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.764600000000001</v>
+        <v>-1.4827</v>
       </c>
       <c r="G27" t="n">
         <v>-1.8598</v>
@@ -2530,19 +2530,19 @@
         <v>-7.6319</v>
       </c>
       <c r="I27" t="n">
-        <v>5.772200000000001</v>
+        <v>5.772199999999999</v>
       </c>
       <c r="J27" t="n">
         <v>6.1952</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.624400000000001</v>
+        <v>-2.6244</v>
       </c>
       <c r="L27" t="n">
         <v>8.819599999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>-8.055099999999999</v>
+        <v>-8.055100000000001</v>
       </c>
       <c r="N27" t="n">
         <v>-5.0074</v>
@@ -2560,13 +2560,13 @@
         <v>9.1629</v>
       </c>
       <c r="S27" t="n">
-        <v>6.2255</v>
+        <v>7.5076</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2526999999999999</v>
+        <v>0.2529</v>
       </c>
       <c r="U27" t="n">
-        <v>5.9725</v>
+        <v>7.254700000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-6.0129</v>
